--- a/data/RKT.MI.xlsx
+++ b/data/RKT.MI.xlsx
@@ -26891,6 +26891,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1154">
+      <c r="A1154" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B1154" t="n">
+        <v>12000</v>
+      </c>
+      <c r="C1154" t="n">
+        <v>0.389999985694885</v>
+      </c>
+      <c r="D1154" t="n">
+        <v>0.375999987125397</v>
+      </c>
+      <c r="E1154" t="n">
+        <v>0.389999985694885</v>
+      </c>
+      <c r="F1154" t="n">
+        <v>0.375999987125397</v>
+      </c>
+      <c r="G1154" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RKT.MI.xlsx
+++ b/data/RKT.MI.xlsx
@@ -26914,6 +26914,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1155">
+      <c r="A1155" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B1155" t="n">
+        <v>70000</v>
+      </c>
+      <c r="C1155" t="n">
+        <v>0.412000000476837</v>
+      </c>
+      <c r="D1155" t="n">
+        <v>0.375999987125397</v>
+      </c>
+      <c r="E1155" t="n">
+        <v>0.375999987125397</v>
+      </c>
+      <c r="F1155" t="n">
+        <v>0.412000000476837</v>
+      </c>
+      <c r="G1155" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RKT.MI.xlsx
+++ b/data/RKT.MI.xlsx
@@ -26937,6 +26937,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1156">
+      <c r="A1156" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B1156" t="n">
+        <v>66000</v>
+      </c>
+      <c r="C1156" t="n">
+        <v>0.421999990940094</v>
+      </c>
+      <c r="D1156" t="n">
+        <v>0.391999989748001</v>
+      </c>
+      <c r="E1156" t="n">
+        <v>0.421999990940094</v>
+      </c>
+      <c r="F1156" t="n">
+        <v>0.391999989748001</v>
+      </c>
+      <c r="G1156" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RKT.MI.xlsx
+++ b/data/RKT.MI.xlsx
@@ -26960,6 +26960,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1157">
+      <c r="A1157" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B1157" t="n">
+        <v>16000</v>
+      </c>
+      <c r="C1157" t="n">
+        <v>0.421999990940094</v>
+      </c>
+      <c r="D1157" t="n">
+        <v>0.398000001907349</v>
+      </c>
+      <c r="E1157" t="n">
+        <v>0.398000001907349</v>
+      </c>
+      <c r="F1157" t="n">
+        <v>0.421999990940094</v>
+      </c>
+      <c r="G1157" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RKT.MI.xlsx
+++ b/data/RKT.MI.xlsx
@@ -26801,22 +26801,22 @@
     </row>
     <row r="1150">
       <c r="A1150" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B1150" t="n">
         <v>12000</v>
       </c>
       <c r="C1150" t="n">
-        <v>0.391999989748001</v>
+        <v>0.375999987125397</v>
       </c>
       <c r="D1150" t="n">
-        <v>0.372000008821487</v>
+        <v>0.356000006198883</v>
       </c>
       <c r="E1150" t="n">
-        <v>0.381999999284744</v>
+        <v>0.356000006198883</v>
       </c>
       <c r="F1150" t="n">
-        <v>0.381999999284744</v>
+        <v>0.375999987125397</v>
       </c>
       <c r="G1150" t="s">
         <v>7</v>
@@ -26824,22 +26824,22 @@
     </row>
     <row r="1151">
       <c r="A1151" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B1151" t="n">
-        <v>8000</v>
+        <v>12000</v>
       </c>
       <c r="C1151" t="n">
-        <v>0.395999997854233</v>
+        <v>0.391999989748001</v>
       </c>
       <c r="D1151" t="n">
-        <v>0.388000011444092</v>
+        <v>0.372000008821487</v>
       </c>
       <c r="E1151" t="n">
-        <v>0.388000011444092</v>
+        <v>0.381999999284744</v>
       </c>
       <c r="F1151" t="n">
-        <v>0.395999997854233</v>
+        <v>0.381999999284744</v>
       </c>
       <c r="G1151" t="s">
         <v>7</v>
@@ -26847,19 +26847,19 @@
     </row>
     <row r="1152">
       <c r="A1152" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B1152" t="n">
-        <v>12000</v>
+        <v>8000</v>
       </c>
       <c r="C1152" t="n">
         <v>0.395999997854233</v>
       </c>
       <c r="D1152" t="n">
-        <v>0.38400000333786</v>
+        <v>0.388000011444092</v>
       </c>
       <c r="E1152" t="n">
-        <v>0.393999993801117</v>
+        <v>0.388000011444092</v>
       </c>
       <c r="F1152" t="n">
         <v>0.395999997854233</v>
@@ -26870,22 +26870,22 @@
     </row>
     <row r="1153">
       <c r="A1153" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B1153" t="n">
-        <v>34000</v>
+        <v>12000</v>
       </c>
       <c r="C1153" t="n">
-        <v>0.412000000476837</v>
+        <v>0.395999997854233</v>
       </c>
       <c r="D1153" t="n">
+        <v>0.38400000333786</v>
+      </c>
+      <c r="E1153" t="n">
         <v>0.393999993801117</v>
       </c>
-      <c r="E1153" t="n">
+      <c r="F1153" t="n">
         <v>0.395999997854233</v>
-      </c>
-      <c r="F1153" t="n">
-        <v>0.400000005960464</v>
       </c>
       <c r="G1153" t="s">
         <v>7</v>
@@ -26893,22 +26893,22 @@
     </row>
     <row r="1154">
       <c r="A1154" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B1154" t="n">
-        <v>12000</v>
+        <v>34000</v>
       </c>
       <c r="C1154" t="n">
-        <v>0.389999985694885</v>
+        <v>0.412000000476837</v>
       </c>
       <c r="D1154" t="n">
-        <v>0.375999987125397</v>
+        <v>0.393999993801117</v>
       </c>
       <c r="E1154" t="n">
-        <v>0.389999985694885</v>
+        <v>0.395999997854233</v>
       </c>
       <c r="F1154" t="n">
-        <v>0.375999987125397</v>
+        <v>0.400000005960464</v>
       </c>
       <c r="G1154" t="s">
         <v>7</v>
@@ -26916,22 +26916,22 @@
     </row>
     <row r="1155">
       <c r="A1155" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B1155" t="n">
-        <v>70000</v>
+        <v>12000</v>
       </c>
       <c r="C1155" t="n">
-        <v>0.412000000476837</v>
+        <v>0.389999985694885</v>
       </c>
       <c r="D1155" t="n">
         <v>0.375999987125397</v>
       </c>
       <c r="E1155" t="n">
+        <v>0.389999985694885</v>
+      </c>
+      <c r="F1155" t="n">
         <v>0.375999987125397</v>
-      </c>
-      <c r="F1155" t="n">
-        <v>0.412000000476837</v>
       </c>
       <c r="G1155" t="s">
         <v>7</v>
@@ -26939,22 +26939,22 @@
     </row>
     <row r="1156">
       <c r="A1156" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B1156" t="n">
-        <v>66000</v>
+        <v>70000</v>
       </c>
       <c r="C1156" t="n">
-        <v>0.421999990940094</v>
+        <v>0.412000000476837</v>
       </c>
       <c r="D1156" t="n">
-        <v>0.391999989748001</v>
+        <v>0.375999987125397</v>
       </c>
       <c r="E1156" t="n">
-        <v>0.421999990940094</v>
+        <v>0.375999987125397</v>
       </c>
       <c r="F1156" t="n">
-        <v>0.391999989748001</v>
+        <v>0.412000000476837</v>
       </c>
       <c r="G1156" t="s">
         <v>7</v>
@@ -26962,24 +26962,47 @@
     </row>
     <row r="1157">
       <c r="A1157" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B1157" t="n">
-        <v>16000</v>
+        <v>66000</v>
       </c>
       <c r="C1157" t="n">
         <v>0.421999990940094</v>
       </c>
       <c r="D1157" t="n">
-        <v>0.398000001907349</v>
+        <v>0.391999989748001</v>
       </c>
       <c r="E1157" t="n">
-        <v>0.398000001907349</v>
+        <v>0.421999990940094</v>
       </c>
       <c r="F1157" t="n">
-        <v>0.421999990940094</v>
+        <v>0.391999989748001</v>
       </c>
       <c r="G1157" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1158">
+      <c r="A1158" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B1158" t="n">
+        <v>98000</v>
+      </c>
+      <c r="C1158" t="n">
+        <v>0.425999999046326</v>
+      </c>
+      <c r="D1158" t="n">
+        <v>0.395999997854233</v>
+      </c>
+      <c r="E1158" t="n">
+        <v>0.412000000476837</v>
+      </c>
+      <c r="F1158" t="n">
+        <v>0.416000008583069</v>
+      </c>
+      <c r="G1158" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/RKT.MI.xlsx
+++ b/data/RKT.MI.xlsx
@@ -26985,24 +26985,47 @@
     </row>
     <row r="1158">
       <c r="A1158" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B1158" t="n">
+        <v>16000</v>
+      </c>
+      <c r="C1158" t="n">
+        <v>0.421999990940094</v>
+      </c>
+      <c r="D1158" t="n">
+        <v>0.398000001907349</v>
+      </c>
+      <c r="E1158" t="n">
+        <v>0.398000001907349</v>
+      </c>
+      <c r="F1158" t="n">
+        <v>0.421999990940094</v>
+      </c>
+      <c r="G1158" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1159">
+      <c r="A1159" s="1" t="n">
         <v>46283.2916666667</v>
       </c>
-      <c r="B1158" t="n">
+      <c r="B1159" t="n">
         <v>98000</v>
       </c>
-      <c r="C1158" t="n">
+      <c r="C1159" t="n">
         <v>0.425999999046326</v>
       </c>
-      <c r="D1158" t="n">
+      <c r="D1159" t="n">
         <v>0.395999997854233</v>
       </c>
-      <c r="E1158" t="n">
+      <c r="E1159" t="n">
         <v>0.412000000476837</v>
       </c>
-      <c r="F1158" t="n">
+      <c r="F1159" t="n">
         <v>0.416000008583069</v>
       </c>
-      <c r="G1158" t="s">
+      <c r="G1159" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/RKT.MI.xlsx
+++ b/data/RKT.MI.xlsx
@@ -30561,6 +30561,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1162">
+      <c r="A1162" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B1162" t="n">
+        <v>42000</v>
+      </c>
+      <c r="C1162" t="n">
+        <v>0.416000008583069</v>
+      </c>
+      <c r="D1162" t="n">
+        <v>0.395999997854233</v>
+      </c>
+      <c r="E1162" t="n">
+        <v>0.404000014066696</v>
+      </c>
+      <c r="F1162" t="n">
+        <v>0.391999989748001</v>
+      </c>
+      <c r="G1162" t="n">
+        <v>0.391999989748001</v>
+      </c>
+      <c r="H1162" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RKT.MI.xlsx
+++ b/data/RKT.MI.xlsx
@@ -30572,7 +30572,7 @@
         <v>0.416000008583069</v>
       </c>
       <c r="D1162" t="n">
-        <v>0.395999997854233</v>
+        <v>0.391999989748001</v>
       </c>
       <c r="E1162" t="n">
         <v>0.404000014066696</v>
@@ -30584,6 +30584,32 @@
         <v>0.391999989748001</v>
       </c>
       <c r="H1162" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1163">
+      <c r="A1163" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B1163" t="n">
+        <v>12000</v>
+      </c>
+      <c r="C1163" t="n">
+        <v>0.391999989748001</v>
+      </c>
+      <c r="D1163" t="n">
+        <v>0.386000007390976</v>
+      </c>
+      <c r="E1163" t="n">
+        <v>0.386000007390976</v>
+      </c>
+      <c r="F1163" t="n">
+        <v>0.391999989748001</v>
+      </c>
+      <c r="G1163" t="n">
+        <v>0.391999989748001</v>
+      </c>
+      <c r="H1163" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/RKT.MI.xlsx
+++ b/data/RKT.MI.xlsx
@@ -30613,6 +30613,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1164">
+      <c r="A1164" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B1164" t="n">
+        <v>124000</v>
+      </c>
+      <c r="C1164" t="n">
+        <v>0.439999997615814</v>
+      </c>
+      <c r="D1164" t="n">
+        <v>0.391999989748001</v>
+      </c>
+      <c r="E1164" t="n">
+        <v>0.398000001907349</v>
+      </c>
+      <c r="F1164" t="n">
+        <v>0.430000007152557</v>
+      </c>
+      <c r="G1164" t="n">
+        <v>0.430000007152557</v>
+      </c>
+      <c r="H1164" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RKT.MI.xlsx
+++ b/data/RKT.MI.xlsx
@@ -30691,6 +30691,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1167">
+      <c r="A1167" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B1167" t="n">
+        <v>8000</v>
+      </c>
+      <c r="C1167" t="n">
+        <v>0.421999990940094</v>
+      </c>
+      <c r="D1167" t="n">
+        <v>0.412000000476837</v>
+      </c>
+      <c r="E1167" t="n">
+        <v>0.421999990940094</v>
+      </c>
+      <c r="F1167" t="n">
+        <v>0.412000000476837</v>
+      </c>
+      <c r="G1167" t="n">
+        <v>0.412000000476837</v>
+      </c>
+      <c r="H1167" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RKT.MI.xlsx
+++ b/data/RKT.MI.xlsx
@@ -27275,8 +27275,31 @@
       <c r="E1170" t="n">
         <v>0.418000012636185</v>
       </c>
-      <c r="F1170"/>
+      <c r="F1170" t="n">
+        <v>0.404000014066696</v>
+      </c>
       <c r="G1170" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1171">
+      <c r="A1171" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B1171" t="n">
+        <v>8000</v>
+      </c>
+      <c r="C1171" t="n">
+        <v>0.395999997854233</v>
+      </c>
+      <c r="D1171" t="n">
+        <v>0.386000007390976</v>
+      </c>
+      <c r="E1171" t="n">
+        <v>0.395999997854233</v>
+      </c>
+      <c r="F1171"/>
+      <c r="G1171" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/RKT.MI.xlsx
+++ b/data/RKT.MI.xlsx
@@ -27298,8 +27298,31 @@
       <c r="E1171" t="n">
         <v>0.395999997854233</v>
       </c>
-      <c r="F1171"/>
+      <c r="F1171" t="n">
+        <v>0.386000007390976</v>
+      </c>
       <c r="G1171" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1172">
+      <c r="A1172" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B1172" t="n">
+        <v>8000</v>
+      </c>
+      <c r="C1172" t="n">
+        <v>0.391999989748001</v>
+      </c>
+      <c r="D1172" t="n">
+        <v>0.391999989748001</v>
+      </c>
+      <c r="E1172" t="n">
+        <v>0.391999989748001</v>
+      </c>
+      <c r="F1172"/>
+      <c r="G1172" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/RKT.MI.xlsx
+++ b/data/RKT.MI.xlsx
@@ -27321,8 +27321,31 @@
       <c r="E1172" t="n">
         <v>0.391999989748001</v>
       </c>
-      <c r="F1172"/>
+      <c r="F1172" t="n">
+        <v>0.391999989748001</v>
+      </c>
       <c r="G1172" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1173">
+      <c r="A1173" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B1173" t="n">
+        <v>4000</v>
+      </c>
+      <c r="C1173" t="n">
+        <v>0.386000007390976</v>
+      </c>
+      <c r="D1173" t="n">
+        <v>0.381999999284744</v>
+      </c>
+      <c r="E1173" t="n">
+        <v>0.381999999284744</v>
+      </c>
+      <c r="F1173"/>
+      <c r="G1173" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/RKT.MI.xlsx
+++ b/data/RKT.MI.xlsx
@@ -27344,8 +27344,31 @@
       <c r="E1173" t="n">
         <v>0.381999999284744</v>
       </c>
-      <c r="F1173"/>
+      <c r="F1173" t="n">
+        <v>0.386000007390976</v>
+      </c>
       <c r="G1173" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1174">
+      <c r="A1174" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B1174" t="n">
+        <v>14000</v>
+      </c>
+      <c r="C1174" t="n">
+        <v>0.379999995231628</v>
+      </c>
+      <c r="D1174" t="n">
+        <v>0.375999987125397</v>
+      </c>
+      <c r="E1174" t="n">
+        <v>0.375999987125397</v>
+      </c>
+      <c r="F1174"/>
+      <c r="G1174" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/RKT.MI.xlsx
+++ b/data/RKT.MI.xlsx
@@ -27374,6 +27374,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1175">
+      <c r="A1175" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B1175" t="n">
+        <v>14000</v>
+      </c>
+      <c r="C1175" t="n">
+        <v>0.374000012874603</v>
+      </c>
+      <c r="D1175" t="n">
+        <v>0.370000004768372</v>
+      </c>
+      <c r="E1175" t="n">
+        <v>0.370000004768372</v>
+      </c>
+      <c r="F1175" t="n">
+        <v>0.374000012874603</v>
+      </c>
+      <c r="G1175" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RKT.MI.xlsx
+++ b/data/RKT.MI.xlsx
@@ -30977,6 +30977,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1178">
+      <c r="A1178" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B1178" t="n">
+        <v>68000</v>
+      </c>
+      <c r="C1178" t="n">
+        <v>0.381999999284744</v>
+      </c>
+      <c r="D1178" t="n">
+        <v>0.354000002145767</v>
+      </c>
+      <c r="E1178" t="n">
+        <v>0.372000008821487</v>
+      </c>
+      <c r="F1178" t="n">
+        <v>0.370000004768372</v>
+      </c>
+      <c r="G1178" t="n">
+        <v>0.370000004768372</v>
+      </c>
+      <c r="H1178" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RKT.MI.xlsx
+++ b/data/RKT.MI.xlsx
@@ -31003,6 +31003,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1179">
+      <c r="A1179" s="1" t="n">
+        <v>46311.2916666667</v>
+      </c>
+      <c r="B1179" t="n">
+        <v>18000</v>
+      </c>
+      <c r="C1179" t="n">
+        <v>0.375999987125397</v>
+      </c>
+      <c r="D1179" t="n">
+        <v>0.361999988555908</v>
+      </c>
+      <c r="E1179" t="n">
+        <v>0.361999988555908</v>
+      </c>
+      <c r="F1179" t="n">
+        <v>0.375999987125397</v>
+      </c>
+      <c r="G1179" t="n">
+        <v>0.375999987125397</v>
+      </c>
+      <c r="H1179" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RKT.MI.xlsx
+++ b/data/RKT.MI.xlsx
@@ -34569,6 +34569,64 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1180">
+      <c r="A1180" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1180" s="1" t="n">
+        <v>46314.2916666667</v>
+      </c>
+      <c r="C1180" t="n">
+        <v>0.368000000715256</v>
+      </c>
+      <c r="D1180" t="n">
+        <v>0.379999995231628</v>
+      </c>
+      <c r="E1180" t="n">
+        <v>0.360000014305115</v>
+      </c>
+      <c r="F1180" t="n">
+        <v>0.379999995231628</v>
+      </c>
+      <c r="G1180" t="n">
+        <v>0.379999995231628</v>
+      </c>
+      <c r="H1180" t="n">
+        <v>14000</v>
+      </c>
+      <c r="I1180" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1181">
+      <c r="A1181" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1181" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C1181" t="n">
+        <v>0.372000008821487</v>
+      </c>
+      <c r="D1181" t="n">
+        <v>0.372000008821487</v>
+      </c>
+      <c r="E1181" t="n">
+        <v>0.363999992609024</v>
+      </c>
+      <c r="F1181" t="n">
+        <v>0.386000007390976</v>
+      </c>
+      <c r="G1181" t="n">
+        <v>0.386000007390976</v>
+      </c>
+      <c r="H1181" t="n">
+        <v>14000</v>
+      </c>
+      <c r="I1181" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RKT.MI.xlsx
+++ b/data/RKT.MI.xlsx
@@ -34609,7 +34609,7 @@
         <v>0.372000008821487</v>
       </c>
       <c r="D1181" t="n">
-        <v>0.372000008821487</v>
+        <v>0.386000007390976</v>
       </c>
       <c r="E1181" t="n">
         <v>0.363999992609024</v>
@@ -34624,6 +34624,35 @@
         <v>14000</v>
       </c>
       <c r="I1181" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1182">
+      <c r="A1182" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1182" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C1182" t="n">
+        <v>0.377999991178513</v>
+      </c>
+      <c r="D1182" t="n">
+        <v>0.377999991178513</v>
+      </c>
+      <c r="E1182" t="n">
+        <v>0.377999991178513</v>
+      </c>
+      <c r="F1182" t="n">
+        <v>0.389999985694885</v>
+      </c>
+      <c r="G1182" t="n">
+        <v>0.389999985694885</v>
+      </c>
+      <c r="H1182" t="n">
+        <v>8000</v>
+      </c>
+      <c r="I1182" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/RKT.MI.xlsx
+++ b/data/RKT.MI.xlsx
@@ -34638,7 +34638,7 @@
         <v>0.377999991178513</v>
       </c>
       <c r="D1182" t="n">
-        <v>0.377999991178513</v>
+        <v>0.389999985694885</v>
       </c>
       <c r="E1182" t="n">
         <v>0.377999991178513</v>
@@ -34653,6 +34653,35 @@
         <v>8000</v>
       </c>
       <c r="I1182" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1183">
+      <c r="A1183" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1183" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C1183" t="n">
+        <v>0.381999999284744</v>
+      </c>
+      <c r="D1183" t="n">
+        <v>0.389999985694885</v>
+      </c>
+      <c r="E1183" t="n">
+        <v>0.374000012874603</v>
+      </c>
+      <c r="F1183" t="n">
+        <v>0.389999985694885</v>
+      </c>
+      <c r="G1183" t="n">
+        <v>0.389999985694885</v>
+      </c>
+      <c r="H1183" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I1183" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/RKT.MI.xlsx
+++ b/data/RKT.MI.xlsx
@@ -34685,6 +34685,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1184">
+      <c r="A1184" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1184" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C1184" t="n">
+        <v>0.381999999284744</v>
+      </c>
+      <c r="D1184" t="n">
+        <v>0.381999999284744</v>
+      </c>
+      <c r="E1184" t="n">
+        <v>0.36599999666214</v>
+      </c>
+      <c r="F1184" t="n">
+        <v>0.375999987125397</v>
+      </c>
+      <c r="G1184" t="n">
+        <v>0.375999987125397</v>
+      </c>
+      <c r="H1184" t="n">
+        <v>28000</v>
+      </c>
+      <c r="I1184" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RKT.MI.xlsx
+++ b/data/RKT.MI.xlsx
@@ -34714,6 +34714,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1185">
+      <c r="A1185" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1185" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C1185" t="n">
+        <v>0.379999995231628</v>
+      </c>
+      <c r="D1185" t="n">
+        <v>0.398000001907349</v>
+      </c>
+      <c r="E1185" t="n">
+        <v>0.368000000715256</v>
+      </c>
+      <c r="F1185" t="n">
+        <v>0.375999987125397</v>
+      </c>
+      <c r="G1185" t="n">
+        <v>0.375999987125397</v>
+      </c>
+      <c r="H1185" t="n">
+        <v>18000</v>
+      </c>
+      <c r="I1185" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RKT.MI.xlsx
+++ b/data/RKT.MI.xlsx
@@ -34743,6 +34743,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1186">
+      <c r="A1186" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1186" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C1186" t="n">
+        <v>0.381999999284744</v>
+      </c>
+      <c r="D1186" t="n">
+        <v>0.398000001907349</v>
+      </c>
+      <c r="E1186" t="n">
+        <v>0.370000004768372</v>
+      </c>
+      <c r="F1186" t="n">
+        <v>0.395999997854233</v>
+      </c>
+      <c r="G1186" t="n">
+        <v>0.395999997854233</v>
+      </c>
+      <c r="H1186" t="n">
+        <v>90000</v>
+      </c>
+      <c r="I1186" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RKT.MI.xlsx
+++ b/data/RKT.MI.xlsx
@@ -34772,6 +34772,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1187">
+      <c r="A1187" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1187" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C1187" t="n">
+        <v>0.386000007390976</v>
+      </c>
+      <c r="D1187" t="n">
+        <v>0.386000007390976</v>
+      </c>
+      <c r="E1187" t="n">
+        <v>0.360000014305115</v>
+      </c>
+      <c r="F1187" t="n">
+        <v>0.391999989748001</v>
+      </c>
+      <c r="G1187" t="n">
+        <v>0.391999989748001</v>
+      </c>
+      <c r="H1187" t="n">
+        <v>222000</v>
+      </c>
+      <c r="I1187" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RKT.MI.xlsx
+++ b/data/RKT.MI.xlsx
@@ -34783,7 +34783,7 @@
         <v>0.386000007390976</v>
       </c>
       <c r="D1187" t="n">
-        <v>0.386000007390976</v>
+        <v>0.391999989748001</v>
       </c>
       <c r="E1187" t="n">
         <v>0.360000014305115</v>
@@ -34795,9 +34795,38 @@
         <v>0.391999989748001</v>
       </c>
       <c r="H1187" t="n">
-        <v>222000</v>
+        <v>228000</v>
       </c>
       <c r="I1187" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1188">
+      <c r="A1188" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1188" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C1188" t="n">
+        <v>0.379999995231628</v>
+      </c>
+      <c r="D1188" t="n">
+        <v>0.418000012636185</v>
+      </c>
+      <c r="E1188" t="n">
+        <v>0.379999995231628</v>
+      </c>
+      <c r="F1188" t="n">
+        <v>0.416000008583069</v>
+      </c>
+      <c r="G1188" t="n">
+        <v>0.416000008583069</v>
+      </c>
+      <c r="H1188" t="n">
+        <v>42000</v>
+      </c>
+      <c r="I1188" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/RKT.MI.xlsx
+++ b/data/RKT.MI.xlsx
@@ -34830,6 +34830,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1189">
+      <c r="A1189" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1189" s="1" t="n">
+        <v>46325.3333333333</v>
+      </c>
+      <c r="C1189" t="n">
+        <v>0.404000014066696</v>
+      </c>
+      <c r="D1189" t="n">
+        <v>0.404000014066696</v>
+      </c>
+      <c r="E1189" t="n">
+        <v>0.38400000333786</v>
+      </c>
+      <c r="F1189" t="n">
+        <v>0.418000012636185</v>
+      </c>
+      <c r="G1189" t="n">
+        <v>0.418000012636185</v>
+      </c>
+      <c r="H1189" t="n">
+        <v>44000</v>
+      </c>
+      <c r="I1189" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
